--- a/rules/CORE-000746/negative/01/data/unit-test-coreid-FB5801-negative_01.xlsx
+++ b/rules/CORE-000746/negative/01/data/unit-test-coreid-FB5801-negative_01.xlsx
@@ -1428,7 +1428,7 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">

--- a/rules/CORE-000746/negative/01/data/unit-test-coreid-FB5801-negative_01.xlsx
+++ b/rules/CORE-000746/negative/01/data/unit-test-coreid-FB5801-negative_01.xlsx
@@ -47,7 +47,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +82,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +189,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +681,169 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LATINO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>suppdm.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CETHNIC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SPANISH ORIGIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>suppdm.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CETHNIC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SPANISH ORIGIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>suppdm.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CETHNIC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SPANISH ORIGIN</t>
         </is>
       </c>
     </row>
@@ -686,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,7 +1251,7 @@
           <t>WHITE</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>LATINO</t>
         </is>
@@ -1145,7 +1317,7 @@
 AMERICAN</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t>NOT HISPANIC</t>
         </is>
@@ -1222,6 +1394,69 @@
           <t>XXXXXXX</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2018-06-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0990000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1941-08-14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1234,7 +1469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,7 +1686,7 @@
           <t>Collected Ethnicity</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>SPANISH ORIGIN</t>
         </is>
@@ -1488,12 +1723,49 @@
           <t>Collected Ethnicity</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>SPANISH ORIGIN</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CETHNIC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Collected Ethnicity</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>SPANISH ORIGIN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>CRF</t>
         </is>
